--- a/030_input/30_Construction_Inputs.xlsx
+++ b/030_input/30_Construction_Inputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/Potential_Study_Tool_Prototype/030_input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{47CB3700-5EBB-4A46-A404-12179673EC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBFA6CA8-689C-42C0-A17C-1C7AD2E2F415}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{47CB3700-5EBB-4A46-A404-12179673EC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19C4DB35-652B-476D-A601-6B2E24B5355E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3420" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B9A3EC35-284E-456A-8454-01F0A959EDAE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B9A3EC35-284E-456A-8454-01F0A959EDAE}"/>
   </bookViews>
   <sheets>
     <sheet name="New_Construction" sheetId="1" r:id="rId1"/>
@@ -919,16 +919,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -939,16 +939,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -959,16 +959,16 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -979,16 +979,16 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -999,16 +999,16 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1019,16 +1019,16 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1039,16 +1039,16 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1067,12 +1067,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B011C3FEFFEFCF44990405A8404263A2" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff8dfd3bc83a02ed6a3437faf473449a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8a600ae29b0fcdec2bdff655f54bd0a0" ns2:_="">
     <xsd:import namespace="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
@@ -1216,6 +1210,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA85399F-EA6F-4B92-B23C-1AA47FFFB46C}">
   <ds:schemaRefs>
@@ -1225,22 +1225,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F54A0B5-383C-4984-9767-EEAB1FFBFD21}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4E85B17-597E-44C7-AF2D-6452EE32BA93}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1256,4 +1240,20 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F54A0B5-383C-4984-9767-EEAB1FFBFD21}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/030_input/30_Construction_Inputs.xlsx
+++ b/030_input/30_Construction_Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/Potential_Study_Tool_Prototype/030_input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{47CB3700-5EBB-4A46-A404-12179673EC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19C4DB35-652B-476D-A601-6B2E24B5355E}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="8_{47CB3700-5EBB-4A46-A404-12179673EC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB31F460-4DFB-492D-AAB3-9D869A6FAB5A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B9A3EC35-284E-456A-8454-01F0A959EDAE}"/>
+    <workbookView xWindow="57480" yWindow="-3420" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B9A3EC35-284E-456A-8454-01F0A959EDAE}"/>
   </bookViews>
   <sheets>
     <sheet name="New_Construction" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <author>Andrew Johnson</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{46AD0563-61F4-4264-9D39-F02C86051E5A}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{691F17E5-B473-46C2-BA96-A5296AB62D06}">
       <text>
         <r>
           <rPr>
@@ -95,7 +95,7 @@
     <author>Andrew Johnson</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{C37A8A0B-449E-43BA-ACB1-BCA46589FE1C}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{720CD0AC-2B17-4C59-A604-B9AFD2984935}">
       <text>
         <r>
           <rPr>
@@ -127,15 +127,9 @@
     <t>single_family</t>
   </si>
   <si>
-    <t>multi_family</t>
-  </si>
-  <si>
     <t>single_family_li</t>
   </si>
   <si>
-    <t>multi_family_li</t>
-  </si>
-  <si>
     <t>heating_cooling</t>
   </si>
   <si>
@@ -164,13 +158,26 @@
   </si>
   <si>
     <t>none</t>
+  </si>
+  <si>
+    <t>multifamily</t>
+  </si>
+  <si>
+    <t>multifamily_li</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,15 +203,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -541,6 +551,7 @@
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -554,152 +565,152 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -725,152 +736,152 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -902,153 +913,153 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.05</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
+      <c r="C3" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.05</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.05</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.05</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.05</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.05</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -1058,12 +1069,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1211,15 +1219,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA85399F-EA6F-4B92-B23C-1AA47FFFB46C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F54A0B5-383C-4984-9767-EEAB1FFBFD21}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1243,17 +1262,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F54A0B5-383C-4984-9767-EEAB1FFBFD21}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA85399F-EA6F-4B92-B23C-1AA47FFFB46C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/030_input/30_Construction_Inputs.xlsx
+++ b/030_input/30_Construction_Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/Potential_Study_Tool_Prototype/030_input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="8_{47CB3700-5EBB-4A46-A404-12179673EC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB31F460-4DFB-492D-AAB3-9D869A6FAB5A}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="8_{47CB3700-5EBB-4A46-A404-12179673EC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB3BDE4D-64E3-49A5-B543-08469061CA78}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-3420" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B9A3EC35-284E-456A-8454-01F0A959EDAE}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{B9A3EC35-284E-456A-8454-01F0A959EDAE}"/>
   </bookViews>
   <sheets>
     <sheet name="New_Construction" sheetId="1" r:id="rId1"/>
@@ -930,16 +930,16 @@
         <v>5</v>
       </c>
       <c r="C2" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -950,16 +950,16 @@
         <v>6</v>
       </c>
       <c r="C3" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -970,16 +970,16 @@
         <v>7</v>
       </c>
       <c r="C4" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -990,16 +990,16 @@
         <v>8</v>
       </c>
       <c r="C5" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1010,16 +1010,16 @@
         <v>9</v>
       </c>
       <c r="C6" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1030,16 +1030,16 @@
         <v>11</v>
       </c>
       <c r="C7" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1050,16 +1050,16 @@
         <v>13</v>
       </c>
       <c r="C8" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1075,6 +1075,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B011C3FEFFEFCF44990405A8404263A2" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff8dfd3bc83a02ed6a3437faf473449a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8a600ae29b0fcdec2bdff655f54bd0a0" ns2:_="">
     <xsd:import namespace="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
@@ -1218,15 +1227,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F54A0B5-383C-4984-9767-EEAB1FFBFD21}">
   <ds:schemaRefs>
@@ -1244,6 +1244,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA85399F-EA6F-4B92-B23C-1AA47FFFB46C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4E85B17-597E-44C7-AF2D-6452EE32BA93}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1259,12 +1267,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA85399F-EA6F-4B92-B23C-1AA47FFFB46C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>